--- a/public/sap-reporting/expansion-150-downloads/EXT-FI21-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI21-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R5480f4c214c94184"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R4a042552016f40bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R1802d5c2f078470d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rad01aed7ea874324"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rcd1078a5c844479f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R6377fc1d708c4383"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -497,7 +497,7 @@
         <x:v>15.09.2026</x:v>
       </x:c>
       <x:c r="I7" s="2" t="str">
-        <x:v>100.00</x:v>
+        <x:v>15.00</x:v>
       </x:c>
       <x:c r="J7" s="2" t="str">
         <x:v>100.00</x:v>
@@ -518,7 +518,7 @@
         <x:v>15.09.2026</x:v>
       </x:c>
       <x:c r="P7" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>100.00</x:v>
       </x:c>
       <x:c r="Q7" s="2" t="str">
         <x:v>OPEN</x:v>
@@ -572,7 +572,7 @@
         <x:v>16.09.2026</x:v>
       </x:c>
       <x:c r="P8" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="Q8" s="2" t="str">
         <x:v>EXCEPTION</x:v>
@@ -628,7 +628,7 @@
         <x:v>17.09.2026</x:v>
       </x:c>
       <x:c r="P9" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="Q9" s="2" t="str">
         <x:v>REVIEW</x:v>
@@ -684,7 +684,7 @@
         <x:v>15.09.2026</x:v>
       </x:c>
       <x:c r="P10" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="Q10" s="2" t="str">
         <x:v>DUPLICATE_TEST</x:v>
@@ -814,7 +814,7 @@
         <x:v>15.09.2026</x:v>
       </x:c>
       <x:c r="I2" s="2" t="str">
-        <x:v>100.00</x:v>
+        <x:v>15.00</x:v>
       </x:c>
       <x:c r="J2" s="2" t="str">
         <x:v>100.00</x:v>
@@ -835,7 +835,7 @@
         <x:v>15.09.2026</x:v>
       </x:c>
       <x:c r="P2" s="2" t="str">
-        <x:v>0000100001</x:v>
+        <x:v>100.00</x:v>
       </x:c>
       <x:c r="Q2" s="2" t="str">
         <x:v>OPEN</x:v>
@@ -889,7 +889,7 @@
         <x:v>16.09.2026</x:v>
       </x:c>
       <x:c r="P3" s="2" t="str">
-        <x:v>0000100002</x:v>
+        <x:v>125.00</x:v>
       </x:c>
       <x:c r="Q3" s="2" t="str">
         <x:v>EXCEPTION</x:v>
@@ -945,7 +945,7 @@
         <x:v>17.09.2026</x:v>
       </x:c>
       <x:c r="P4" s="2" t="str">
-        <x:v>0000100003</x:v>
+        <x:v>1.234,50</x:v>
       </x:c>
       <x:c r="Q4" s="2" t="str">
         <x:v>REVIEW</x:v>
@@ -1001,7 +1001,7 @@
         <x:v>15.09.2026</x:v>
       </x:c>
       <x:c r="P5" s="2" t="str">
-        <x:v>0000100004</x:v>
+        <x:v>175.00</x:v>
       </x:c>
       <x:c r="Q5" s="2" t="str">
         <x:v>DUPLICATE_TEST</x:v>
@@ -1350,7 +1350,7 @@
         <x:v>Giữ chuỗi RAW dd.MM.yyyy; parse rõ format/locale/timezone. Blank là thiếu ngày, không lấy ngày máy.</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="63" customHeight="1">
+    <x:row r="17" ht="80" customHeight="1">
       <x:c r="A17" s="8" t="str">
         <x:v>16</x:v>
       </x:c>
@@ -1358,7 +1358,7 @@
         <x:v>Dunning Fee</x:v>
       </x:c>
       <x:c r="C17" s="8" t="str">
-        <x:v>text</x:v>
+        <x:v>raw_decimal</x:v>
       </x:c>
       <x:c r="D17" s="8" t="str">
         <x:v>Thuộc tính nghiệp vụ: Dunning Fee. Đọc tại grain của hồ sơ; nhãn và semantics cần đối chiếu hệ công ty.</x:v>
@@ -1367,7 +1367,7 @@
         <x:v>SAVA_PROPOSED / chưa xác minh</x:v>
       </x:c>
       <x:c r="F17" s="8" t="str">
-        <x:v>Giữ ID dạng Text và số0 đầu. Trim trên bản CLEAN riêng, giữ raw value và source-row lineage. Không join bằng tên diễn giải.</x:v>
+        <x:v>Giữ chuỗi RAW và locale. Chuẩn hóa dấu, separator, currency/UoM/price unit trước tính. Blank không là0; không cộng tỷ lệ/đơn giá/snapshot.</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="63" customHeight="1">
